--- a/6.4 Bonaire with disturbances/output/Rugosity_growth_param_0.5.xlsx
+++ b/6.4 Bonaire with disturbances/output/Rugosity_growth_param_0.5.xlsx
@@ -448,7 +448,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.879488650383351</v>
+        <v>1.903707025111165</v>
       </c>
     </row>
     <row r="4">
@@ -456,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.873452245439871</v>
+        <v>1.919635360248771</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.863660411647438</v>
+        <v>1.929101752859614</v>
       </c>
     </row>
     <row r="6">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.870869678582286</v>
+        <v>1.954087746146769</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.638750663765264</v>
+        <v>1.703424798075825</v>
       </c>
     </row>
     <row r="8">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.665654762559277</v>
+        <v>1.739770153566961</v>
       </c>
     </row>
     <row r="9">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.55070953535897</v>
+        <v>1.615021877713238</v>
       </c>
     </row>
     <row r="10">
@@ -504,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.537235409401337</v>
+        <v>1.594257993289982</v>
       </c>
     </row>
     <row r="11">
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.571438644315046</v>
+        <v>1.629412083252928</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.613234653141546</v>
+        <v>1.673507961740332</v>
       </c>
     </row>
     <row r="13">
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.673743379931072</v>
+        <v>1.737034144094984</v>
       </c>
     </row>
     <row r="14">
@@ -536,7 +536,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.72793176324456</v>
+        <v>1.793950838639744</v>
       </c>
     </row>
     <row r="15">
@@ -544,7 +544,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.796041274026396</v>
+        <v>1.865694385741872</v>
       </c>
     </row>
   </sheetData>
